--- a/commands/cmos2/cmos2_command_deck.xlsx
+++ b/commands/cmos2/cmos2_command_deck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanasi/Documents/FOXSI/GSE/GSE-FOXSI-4/foxsi4-commands/commands/cmos2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CD1C2A-2129-F840-B14F-076E7BAFEB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60720A9-BA46-C046-8CF0-AA29EE3F4DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="760" windowWidth="30220" windowHeight="17880" xr2:uid="{1DE950B2-129E-5A4D-8896-FB78BBCF4CAC}"/>
+    <workbookView xWindow="20" yWindow="760" windowWidth="30220" windowHeight="17820" xr2:uid="{1DE950B2-129E-5A4D-8896-FB78BBCF4CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="all_systems" sheetId="1" r:id="rId1"/>
@@ -1060,7 +1060,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1128,10 +1128,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1150,9 +1146,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1190,7 +1186,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1296,7 +1292,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1438,7 +1434,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1466,7 +1462,7 @@
     <col min="25" max="25" width="12.83203125" style="20" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.1640625" style="20" customWidth="1"/>
     <col min="27" max="27" width="27.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="27.6640625" style="38" customWidth="1"/>
+    <col min="28" max="29" width="27.6640625" style="20" customWidth="1"/>
     <col min="30" max="30" width="19.1640625" customWidth="1"/>
     <col min="31" max="31" width="73.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1509,8 +1505,8 @@
       </c>
       <c r="Z1" s="35"/>
       <c r="AA1" s="36"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
     </row>
     <row r="2" spans="1:31" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -4793,7 +4789,7 @@
         <v>113</v>
       </c>
       <c r="AB36" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC36" s="3" t="s">
         <v>300</v>
@@ -4889,7 +4885,7 @@
         <v>113</v>
       </c>
       <c r="AB37" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC37" s="3" t="s">
         <v>300</v>
@@ -4985,7 +4981,7 @@
         <v>113</v>
       </c>
       <c r="AB38" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC38" s="3" t="s">
         <v>300</v>
@@ -5177,7 +5173,7 @@
         <v>113</v>
       </c>
       <c r="AB40" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC40" s="3" t="s">
         <v>300</v>
@@ -5561,7 +5557,7 @@
         <v>113</v>
       </c>
       <c r="AB44" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC44" s="3" t="s">
         <v>300</v>
@@ -5657,7 +5653,7 @@
         <v>113</v>
       </c>
       <c r="AB45" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>300</v>
@@ -5753,7 +5749,7 @@
         <v>113</v>
       </c>
       <c r="AB46" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>302</v>
